--- a/6098.T_settings.xlsx
+++ b/6098.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -478,11 +493,11 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,33 +506,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F2" t="n">
-        <v>74.7400109469075</v>
+        <v>38.46196247818089</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>74.74%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>747,400円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>88日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.273551386464543</v>
+      </c>
+      <c r="I2" t="n">
+        <v>384619.6247818088</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1384619.624781809</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21129.95852640879</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.487696310769532</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -525,11 +541,11 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,33 +554,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F3" t="n">
-        <v>74.7400109469075</v>
+        <v>36.16335693925307</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>74.74%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>747,400円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>88日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.018150771028119</v>
+      </c>
+      <c r="I3" t="n">
+        <v>361633.5693925307</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1361633.569392531</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20795.79792061761</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.487696310769532</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -576,7 +593,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,33 +602,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F4" t="n">
-        <v>74.7400109469075</v>
+        <v>36.16335693925307</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>74.74%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>747,400円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>88日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.018150771028119</v>
+      </c>
+      <c r="I4" t="n">
+        <v>361633.5693925307</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1361633.569392531</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20795.79792061761</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.487696310769532</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -628,37 +646,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>68.89300357095622</v>
+        <v>29.36549125547437</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>68.89%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>688,930円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>89日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.835343203467148</v>
+      </c>
+      <c r="I5" t="n">
+        <v>293654.9125547437</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1293654.912554744</v>
+      </c>
+      <c r="K5" t="n">
+        <v>37013.50147869908</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26.10352672842225</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +694,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>43.75</v>
       </c>
       <c r="F6" t="n">
-        <v>68.89300357095622</v>
+        <v>27.21789613675852</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>68.89%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>688,930円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>89日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.701118508547408</v>
+      </c>
+      <c r="I6" t="n">
+        <v>272178.9613675852</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1272178.961367585</v>
+      </c>
+      <c r="K6" t="n">
+        <v>36481.99051255218</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.9375</v>
+      </c>
+      <c r="M6" t="n">
+        <v>26.10352672842225</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -722,37 +742,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>43.75</v>
       </c>
       <c r="F7" t="n">
-        <v>68.89300357095622</v>
+        <v>27.21789613675852</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>68.89%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>688,930円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>89日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.701118508547408</v>
+      </c>
+      <c r="I7" t="n">
+        <v>272178.9613675852</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1272178.961367585</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36481.99051255218</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.9375</v>
+      </c>
+      <c r="M7" t="n">
+        <v>26.10352672842225</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -773,33 +794,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F8" t="n">
-        <v>64.13881748071979</v>
+        <v>22.43450660579039</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>641,388円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>68日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.492722956198933</v>
+      </c>
+      <c r="I8" t="n">
+        <v>224345.0660579039</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1224345.066057904</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20118.8600706485</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.555555555555555</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16.48928113598982</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -807,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -820,33 +842,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F9" t="n">
-        <v>64.13881748071979</v>
+        <v>20.40197268814992</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>641,388円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>68日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.26688585423888</v>
+      </c>
+      <c r="I9" t="n">
+        <v>204019.7268814992</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1204019.726881499</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19801.4846993666</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.48928113598982</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -858,7 +881,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -867,33 +890,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F10" t="n">
-        <v>64.13881748071979</v>
+        <v>20.40197268814992</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>641,388円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>68日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.26688585423888</v>
+      </c>
+      <c r="I10" t="n">
+        <v>204019.7268814992</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1204019.726881499</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19801.4846993666</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16.48928113598982</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -901,11 +925,11 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -914,33 +938,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F11" t="n">
-        <v>64.13881748071979</v>
+        <v>12.26104658999946</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>641,388円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>68日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.36233850999994</v>
+      </c>
+      <c r="I11" t="n">
+        <v>122610.4658999946</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1122610.465899995</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21129.175631315</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="M11" t="n">
+        <v>17.79472326915196</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -952,42 +977,43 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="F12" t="n">
-        <v>64.13881748071979</v>
+        <v>11.85547378294601</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>641,388円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>68日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9119595217650774</v>
+      </c>
+      <c r="I12" t="n">
+        <v>118554.7378294601</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1118554.73782946</v>
+      </c>
+      <c r="K12" t="n">
+        <v>29881.80598255922</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.615384615384615</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14.77770008687222</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -995,7 +1021,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1004,37 +1030,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="F13" t="n">
-        <v>64.13881748071979</v>
+        <v>11.85547378294601</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>641,388円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>68日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9119595217650774</v>
+      </c>
+      <c r="I13" t="n">
+        <v>118554.7378294601</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1118554.73782946</v>
+      </c>
+      <c r="K13" t="n">
+        <v>29881.80598255922</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9.615384615384615</v>
+      </c>
+      <c r="M13" t="n">
+        <v>14.77770008687222</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1042,46 +1069,47 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F14" t="n">
-        <v>56.31745598447412</v>
+        <v>11.76127544044091</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>28.16%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>563,175円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>38日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.306808382271212</v>
+      </c>
+      <c r="I14" t="n">
+        <v>117612.7544044091</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1117612.754404409</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20423.12595347192</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.58265501065393</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1089,46 +1117,47 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F15" t="n">
-        <v>56.31745598447412</v>
+        <v>10.39740217185628</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>28.16%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>563,175円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>38日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.155266907984031</v>
+      </c>
+      <c r="I15" t="n">
+        <v>103974.0217185628</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1103974.021718563</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20795.02802235678</v>
+      </c>
+      <c r="L15" t="n">
+        <v>13.11111111111111</v>
+      </c>
+      <c r="M15" t="n">
+        <v>17.79472326915197</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,46 +1165,47 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F16" t="n">
-        <v>56.24105206240611</v>
+        <v>10.39740217185628</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>28.12%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>562,411円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>40日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.155266907984031</v>
+      </c>
+      <c r="I16" t="n">
+        <v>103974.0217185628</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1103974.021718563</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20795.02802235678</v>
+      </c>
+      <c r="L16" t="n">
+        <v>13.11111111111111</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17.79472326915197</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1187,42 +1217,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F17" t="n">
-        <v>39.99122999342249</v>
+        <v>9.905927717736759</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>39.99%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>399,912円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.100658635304084</v>
+      </c>
+      <c r="I17" t="n">
+        <v>99059.27717736759</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1099059.277177368</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20100.69946756585</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9.222222222222221</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10.58265501065394</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1230,46 +1261,47 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F18" t="n">
-        <v>39.99122999342249</v>
+        <v>9.905927717736759</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>39.99%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>399,912円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.100658635304084</v>
+      </c>
+      <c r="I18" t="n">
+        <v>99059.27717736759</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1099059.277177368</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20100.69946756585</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9.222222222222221</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10.58265501065394</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1277,46 +1309,47 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="F19" t="n">
-        <v>39.99122999342249</v>
+        <v>9.665469717745902</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>39.99%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>399,912円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7434976705958386</v>
+      </c>
+      <c r="I19" t="n">
+        <v>96654.69717745902</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1096654.697177459</v>
+      </c>
+      <c r="K19" t="n">
+        <v>30806.76261850062</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9.923076923076923</v>
+      </c>
+      <c r="M19" t="n">
+        <v>19.65667288277962</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1328,42 +1361,43 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="F20" t="n">
-        <v>39.99122999342249</v>
+        <v>9.665469717745902</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>39.99%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>399,912円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7434976705958386</v>
+      </c>
+      <c r="I20" t="n">
+        <v>96654.69717745902</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1096654.697177459</v>
+      </c>
+      <c r="K20" t="n">
+        <v>30806.76261850062</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.923076923076923</v>
+      </c>
+      <c r="M20" t="n">
+        <v>19.65667288277962</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1380,37 +1414,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="F21" t="n">
-        <v>39.99122999342249</v>
+        <v>4.879034560456523</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>39.99%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>399,912円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3753103508043479</v>
+      </c>
+      <c r="I21" t="n">
+        <v>48790.34560456523</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1048790.345604565</v>
+      </c>
+      <c r="K21" t="n">
+        <v>28126.06758329614</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8.384615384615385</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14.77770008687219</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1418,46 +1453,47 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="F22" t="n">
-        <v>39.99122999342249</v>
+        <v>2.825621309645369</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>39.99%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>399,912円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>64日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2173554853573361</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28256.21309645369</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1028256.213096454</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28870.29001336155</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8.692307692307692</v>
+      </c>
+      <c r="M22" t="n">
+        <v>19.65667288277962</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1465,7 +1501,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1478,33 +1514,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-5.26326053529476</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.3759471810924829</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-52632.6053529476</v>
+      </c>
+      <c r="J23" t="n">
+        <v>947367.3946470524</v>
+      </c>
+      <c r="K23" t="n">
+        <v>30071.089549607</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9.642857142857142</v>
+      </c>
+      <c r="M23" t="n">
+        <v>24.96389817562994</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1516,7 +1553,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1525,33 +1562,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-5.26326053529476</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.3759471810924829</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-52632.6053529476</v>
+      </c>
+      <c r="J24" t="n">
+        <v>947367.3946470524</v>
+      </c>
+      <c r="K24" t="n">
+        <v>30071.089549607</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9.642857142857142</v>
+      </c>
+      <c r="M24" t="n">
+        <v>24.96389817562994</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1559,46 +1597,47 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-5.463445611048664</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.4966768737316967</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-54634.45611048664</v>
+      </c>
+      <c r="J25" t="n">
+        <v>945365.5438895134</v>
+      </c>
+      <c r="K25" t="n">
+        <v>23630.17205519007</v>
+      </c>
+      <c r="L25" t="n">
+        <v>9.363636363636363</v>
+      </c>
+      <c r="M25" t="n">
+        <v>23.38326740444044</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1619,33 +1658,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-5.463445611048664</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.4966768737316967</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-54634.45611048664</v>
+      </c>
+      <c r="J26" t="n">
+        <v>945365.5438895134</v>
+      </c>
+      <c r="K26" t="n">
+        <v>23630.17205519007</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.363636363636363</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23.38326740444044</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1653,46 +1693,47 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-5.926535969584889</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.3292519983102716</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-59265.35969584889</v>
+      </c>
+      <c r="J27" t="n">
+        <v>940734.6403041511</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36919.85978223611</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10.38888888888889</v>
+      </c>
+      <c r="M27" t="n">
+        <v>26.40343616744915</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1700,7 +1741,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1713,33 +1754,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-5.926535969584889</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.3292519983102716</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-59265.35969584889</v>
+      </c>
+      <c r="J28" t="n">
+        <v>940734.6403041511</v>
+      </c>
+      <c r="K28" t="n">
+        <v>36919.85978223611</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10.38888888888889</v>
+      </c>
+      <c r="M28" t="n">
+        <v>26.40343616744915</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1747,11 +1789,11 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1760,33 +1802,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-7.076710578844499</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.3931505877135832</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-70767.10578844498</v>
+      </c>
+      <c r="J29" t="n">
+        <v>929232.894211555</v>
+      </c>
+      <c r="K29" t="n">
+        <v>36763.71009264301</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>27.30325313412942</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1794,11 +1837,11 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1807,33 +1850,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-11.17200225941328</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.798000161386663</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-111720.0225941328</v>
+      </c>
+      <c r="J30" t="n">
+        <v>888279.9774058672</v>
+      </c>
+      <c r="K30" t="n">
+        <v>28303.54551172236</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>24.96389817562996</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1841,11 +1885,11 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1854,33 +1898,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-11.35970176814917</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-1.032700160740833</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-113597.0176814917</v>
+      </c>
+      <c r="J31" t="n">
+        <v>886402.9823185083</v>
+      </c>
+      <c r="K31" t="n">
+        <v>22141.30425825898</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.909090909090909</v>
+      </c>
+      <c r="M31" t="n">
+        <v>23.38326740444043</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1892,42 +1937,43 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-13.96795887546826</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.6651408988318217</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-139679.5887546826</v>
+      </c>
+      <c r="J32" t="n">
+        <v>860320.4112453174</v>
+      </c>
+      <c r="K32" t="n">
+        <v>39252.74946218758</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10.52380952380952</v>
+      </c>
+      <c r="M32" t="n">
+        <v>26.42417719637527</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,46 +1981,47 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-13.96795887546826</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.6651408988318217</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-139679.5887546826</v>
+      </c>
+      <c r="J33" t="n">
+        <v>860320.4112453174</v>
+      </c>
+      <c r="K33" t="n">
+        <v>39252.74946218758</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10.52380952380952</v>
+      </c>
+      <c r="M33" t="n">
+        <v>26.42417719637527</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,11 +2029,11 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1995,33 +2042,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-15.01981627547027</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.7152293464509655</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-150198.1627547027</v>
+      </c>
+      <c r="J34" t="n">
+        <v>849801.8372452973</v>
+      </c>
+      <c r="K34" t="n">
+        <v>39089.60330444677</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10.61904761904762</v>
+      </c>
+      <c r="M34" t="n">
+        <v>27.32374057608406</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2033,42 +2081,43 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-17.10182211348048</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.777355550612749</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-171018.2211348048</v>
+      </c>
+      <c r="J35" t="n">
+        <v>828981.7788651952</v>
+      </c>
+      <c r="K35" t="n">
+        <v>40120.62962253331</v>
+      </c>
+      <c r="L35" t="n">
+        <v>10.18181818181818</v>
+      </c>
+      <c r="M35" t="n">
+        <v>26.42417719637526</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2076,46 +2125,47 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-17.10182211348048</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.777355550612749</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-171018.2211348048</v>
+      </c>
+      <c r="J36" t="n">
+        <v>828981.7788651952</v>
+      </c>
+      <c r="K36" t="n">
+        <v>40120.62962253331</v>
+      </c>
+      <c r="L36" t="n">
+        <v>10.18181818181818</v>
+      </c>
+      <c r="M36" t="n">
+        <v>26.42417719637526</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2123,7 +2173,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2132,37 +2182,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-18.11536382092875</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.8234256282240342</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-181153.6382092875</v>
+      </c>
+      <c r="J37" t="n">
+        <v>818846.3617907125</v>
+      </c>
+      <c r="K37" t="n">
+        <v>39963.4263407197</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10.27272727272727</v>
+      </c>
+      <c r="M37" t="n">
+        <v>27.32374057608405</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,11 +2221,11 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2183,33 +2234,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-18.21854294989503</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.9109271474947518</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-182185.4294989504</v>
+      </c>
+      <c r="J38" t="n">
+        <v>817814.5705010496</v>
+      </c>
+      <c r="K38" t="n">
+        <v>41942.14355544751</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>36.08290330837139</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2217,46 +2269,47 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-18.21854294989503</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.9109271474947518</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-182185.4294989504</v>
+      </c>
+      <c r="J39" t="n">
+        <v>817814.5705010496</v>
+      </c>
+      <c r="K39" t="n">
+        <v>41942.14355544751</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M39" t="n">
+        <v>36.08290330837139</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2273,37 +2326,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-19.95447025452879</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1.425319303894913</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-199544.7025452879</v>
+      </c>
+      <c r="J40" t="n">
+        <v>800455.2974547121</v>
+      </c>
+      <c r="K40" t="n">
+        <v>25312.17507938868</v>
+      </c>
+      <c r="L40" t="n">
+        <v>9.642857142857142</v>
+      </c>
+      <c r="M40" t="n">
+        <v>20.0871380906465</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2311,7 +2365,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2320,37 +2374,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-22.24278630127095</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.588770450090782</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-222427.8630127095</v>
+      </c>
+      <c r="J41" t="n">
+        <v>777572.1369872905</v>
+      </c>
+      <c r="K41" t="n">
+        <v>25190.38204782508</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9.785714285714286</v>
+      </c>
+      <c r="M41" t="n">
+        <v>22.37166147164906</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2362,7 +2417,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2371,33 +2426,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-22.26773020735961</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.8564511618215233</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-222677.302073596</v>
+      </c>
+      <c r="J42" t="n">
+        <v>777322.697926404</v>
+      </c>
+      <c r="K42" t="n">
+        <v>45673.14958479366</v>
+      </c>
+      <c r="L42" t="n">
+        <v>8.307692307692308</v>
+      </c>
+      <c r="M42" t="n">
+        <v>31.76996667766071</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2405,46 +2461,47 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-22.26773020735961</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.8564511618215233</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-222677.302073596</v>
+      </c>
+      <c r="J43" t="n">
+        <v>777322.697926404</v>
+      </c>
+      <c r="K43" t="n">
+        <v>45673.14958479366</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8.307692307692308</v>
+      </c>
+      <c r="M43" t="n">
+        <v>31.76996667766071</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2452,46 +2509,47 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-23.19347280787324</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1.656676629133803</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-231934.7280787324</v>
+      </c>
+      <c r="J44" t="n">
+        <v>768065.2719212676</v>
+      </c>
+      <c r="K44" t="n">
+        <v>25093.63388997882</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.928571428571429</v>
+      </c>
+      <c r="M44" t="n">
+        <v>23.3207723059801</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2499,46 +2557,47 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-23.218111741165</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.8930042977371154</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-232181.11741165</v>
+      </c>
+      <c r="J45" t="n">
+        <v>767818.88258835</v>
+      </c>
+      <c r="K45" t="n">
+        <v>45482.96562747855</v>
+      </c>
+      <c r="L45" t="n">
+        <v>8.384615384615385</v>
+      </c>
+      <c r="M45" t="n">
+        <v>32.60417059185823</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2546,46 +2605,47 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-23.31926216676431</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.165963108338215</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-233192.6216676431</v>
+      </c>
+      <c r="J46" t="n">
+        <v>766807.3783323569</v>
+      </c>
+      <c r="K46" t="n">
+        <v>39557.244376616</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>36.0829033083714</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/6098.T_settings.xlsx
+++ b/6098.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>66.66666666666666</v>
       </c>
       <c r="F2" t="n">
-        <v>38.46196247818089</v>
+        <v>38.46198023492224</v>
       </c>
       <c r="G2" t="n">
         <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>4.273551386464543</v>
+        <v>4.273553359435804</v>
       </c>
       <c r="I2" t="n">
-        <v>384619.6247818088</v>
+        <v>384619.8023492224</v>
       </c>
       <c r="J2" t="n">
-        <v>1384619.624781809</v>
+        <v>1384619.802349222</v>
       </c>
       <c r="K2" t="n">
-        <v>21129.95852640879</v>
+        <v>21129.95685482697</v>
       </c>
       <c r="L2" t="n">
         <v>7.666666666666667</v>
       </c>
       <c r="M2" t="n">
-        <v>7.487696310769532</v>
+        <v>7.487687384273125</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F3" t="n">
-        <v>36.16335693925307</v>
+        <v>36.16338767681687</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>4.018150771028119</v>
+        <v>4.018154186312986</v>
       </c>
       <c r="I3" t="n">
-        <v>361633.5693925307</v>
+        <v>361633.8767681688</v>
       </c>
       <c r="J3" t="n">
-        <v>1361633.569392531</v>
+        <v>1361633.876768169</v>
       </c>
       <c r="K3" t="n">
-        <v>20795.79792061761</v>
+        <v>20795.79820673068</v>
       </c>
       <c r="L3" t="n">
         <v>8.444444444444445</v>
       </c>
       <c r="M3" t="n">
-        <v>7.487696310769532</v>
+        <v>7.487687384273118</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F4" t="n">
-        <v>36.16335693925307</v>
+        <v>36.16338767681687</v>
       </c>
       <c r="G4" t="n">
         <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>4.018150771028119</v>
+        <v>4.018154186312986</v>
       </c>
       <c r="I4" t="n">
-        <v>361633.5693925307</v>
+        <v>361633.8767681688</v>
       </c>
       <c r="J4" t="n">
-        <v>1361633.569392531</v>
+        <v>1361633.876768169</v>
       </c>
       <c r="K4" t="n">
-        <v>20795.79792061761</v>
+        <v>20795.79820673068</v>
       </c>
       <c r="L4" t="n">
         <v>8.444444444444445</v>
       </c>
       <c r="M4" t="n">
-        <v>7.487696310769532</v>
+        <v>7.487687384273118</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>29.36549125547437</v>
+        <v>29.3654606281769</v>
       </c>
       <c r="G5" t="n">
         <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>1.835343203467148</v>
+        <v>1.835341289261056</v>
       </c>
       <c r="I5" t="n">
-        <v>293654.9125547437</v>
+        <v>293654.606281769</v>
       </c>
       <c r="J5" t="n">
-        <v>1293654.912554744</v>
+        <v>1293654.606281769</v>
       </c>
       <c r="K5" t="n">
-        <v>37013.50147869908</v>
+        <v>37013.4884843594</v>
       </c>
       <c r="L5" t="n">
         <v>8.5</v>
       </c>
       <c r="M5" t="n">
-        <v>26.10352672842225</v>
+        <v>26.10351242799299</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>43.75</v>
       </c>
       <c r="F6" t="n">
-        <v>27.21789613675852</v>
+        <v>27.21787842134093</v>
       </c>
       <c r="G6" t="n">
         <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>1.701118508547408</v>
+        <v>1.701117401333808</v>
       </c>
       <c r="I6" t="n">
-        <v>272178.9613675852</v>
+        <v>272178.7842134093</v>
       </c>
       <c r="J6" t="n">
-        <v>1272178.961367585</v>
+        <v>1272178.784213409</v>
       </c>
       <c r="K6" t="n">
-        <v>36481.99051255218</v>
+        <v>36481.98078908263</v>
       </c>
       <c r="L6" t="n">
         <v>8.9375</v>
       </c>
       <c r="M6" t="n">
-        <v>26.10352672842225</v>
+        <v>26.103512427993</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>43.75</v>
       </c>
       <c r="F7" t="n">
-        <v>27.21789613675852</v>
+        <v>27.21787842134093</v>
       </c>
       <c r="G7" t="n">
         <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>1.701118508547408</v>
+        <v>1.701117401333808</v>
       </c>
       <c r="I7" t="n">
-        <v>272178.9613675852</v>
+        <v>272178.7842134093</v>
       </c>
       <c r="J7" t="n">
-        <v>1272178.961367585</v>
+        <v>1272178.784213409</v>
       </c>
       <c r="K7" t="n">
-        <v>36481.99051255218</v>
+        <v>36481.98078908263</v>
       </c>
       <c r="L7" t="n">
         <v>8.9375</v>
       </c>
       <c r="M7" t="n">
-        <v>26.10352672842225</v>
+        <v>26.103512427993</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F8" t="n">
-        <v>22.43450660579039</v>
+        <v>22.43453048898238</v>
       </c>
       <c r="G8" t="n">
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.492722956198933</v>
+        <v>2.49272560988693</v>
       </c>
       <c r="I8" t="n">
-        <v>224345.0660579039</v>
+        <v>224345.3048898238</v>
       </c>
       <c r="J8" t="n">
-        <v>1224345.066057904</v>
+        <v>1224345.304889824</v>
       </c>
       <c r="K8" t="n">
-        <v>20118.8600706485</v>
+        <v>20118.85891900705</v>
       </c>
       <c r="L8" t="n">
         <v>9.555555555555555</v>
       </c>
       <c r="M8" t="n">
-        <v>16.48928113598982</v>
+        <v>16.48925537694911</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F9" t="n">
-        <v>20.40197268814992</v>
+        <v>20.40200791376273</v>
       </c>
       <c r="G9" t="n">
         <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26688585423888</v>
+        <v>2.266889768195858</v>
       </c>
       <c r="I9" t="n">
-        <v>204019.7268814992</v>
+        <v>204020.0791376273</v>
       </c>
       <c r="J9" t="n">
-        <v>1204019.726881499</v>
+        <v>1204020.079137627</v>
       </c>
       <c r="K9" t="n">
-        <v>19801.4846993666</v>
+        <v>19801.48539984543</v>
       </c>
       <c r="L9" t="n">
         <v>10.33333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>16.48928113598982</v>
+        <v>16.48925537694911</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F10" t="n">
-        <v>20.40197268814992</v>
+        <v>20.40200791376273</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2.26688585423888</v>
+        <v>2.266889768195858</v>
       </c>
       <c r="I10" t="n">
-        <v>204019.7268814992</v>
+        <v>204020.0791376273</v>
       </c>
       <c r="J10" t="n">
-        <v>1204019.726881499</v>
+        <v>1204020.079137627</v>
       </c>
       <c r="K10" t="n">
-        <v>19801.4846993666</v>
+        <v>19801.48539984543</v>
       </c>
       <c r="L10" t="n">
         <v>10.33333333333333</v>
       </c>
       <c r="M10" t="n">
-        <v>16.48928113598982</v>
+        <v>16.48925537694911</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F11" t="n">
-        <v>12.26104658999946</v>
+        <v>12.26103538710165</v>
       </c>
       <c r="G11" t="n">
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.36233850999994</v>
+        <v>1.362337265233517</v>
       </c>
       <c r="I11" t="n">
-        <v>122610.4658999946</v>
+        <v>122610.3538710165</v>
       </c>
       <c r="J11" t="n">
-        <v>1122610.465899995</v>
+        <v>1122610.353871017</v>
       </c>
       <c r="K11" t="n">
-        <v>21129.175631315</v>
+        <v>21129.17026461756</v>
       </c>
       <c r="L11" t="n">
         <v>12.33333333333333</v>
       </c>
       <c r="M11" t="n">
-        <v>17.79472326915196</v>
+        <v>17.7947141837244</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>46.15384615384615</v>
       </c>
       <c r="F12" t="n">
-        <v>11.85547378294601</v>
+        <v>11.85546321820875</v>
       </c>
       <c r="G12" t="n">
         <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9119595217650774</v>
+        <v>0.9119587090929809</v>
       </c>
       <c r="I12" t="n">
-        <v>118554.7378294601</v>
+        <v>118554.6321820875</v>
       </c>
       <c r="J12" t="n">
-        <v>1118554.73782946</v>
+        <v>1118554.632182088</v>
       </c>
       <c r="K12" t="n">
-        <v>29881.80598255922</v>
+        <v>29881.79924200477</v>
       </c>
       <c r="L12" t="n">
         <v>9.615384615384615</v>
       </c>
       <c r="M12" t="n">
-        <v>14.77770008687222</v>
+        <v>14.77768771534721</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>46.15384615384615</v>
       </c>
       <c r="F13" t="n">
-        <v>11.85547378294601</v>
+        <v>11.85546321820875</v>
       </c>
       <c r="G13" t="n">
         <v>13</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9119595217650774</v>
+        <v>0.9119587090929809</v>
       </c>
       <c r="I13" t="n">
-        <v>118554.7378294601</v>
+        <v>118554.6321820875</v>
       </c>
       <c r="J13" t="n">
-        <v>1118554.73782946</v>
+        <v>1118554.632182088</v>
       </c>
       <c r="K13" t="n">
-        <v>29881.80598255922</v>
+        <v>29881.79924200477</v>
       </c>
       <c r="L13" t="n">
         <v>9.615384615384615</v>
       </c>
       <c r="M13" t="n">
-        <v>14.77770008687222</v>
+        <v>14.77768771534721</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F14" t="n">
-        <v>11.76127544044091</v>
+        <v>11.76130238560697</v>
       </c>
       <c r="G14" t="n">
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.306808382271212</v>
+        <v>1.306811376178552</v>
       </c>
       <c r="I14" t="n">
-        <v>117612.7544044091</v>
+        <v>117613.0238560697</v>
       </c>
       <c r="J14" t="n">
-        <v>1117612.754404409</v>
+        <v>1117613.02385607</v>
       </c>
       <c r="K14" t="n">
-        <v>20423.12595347192</v>
+        <v>20423.12497030544</v>
       </c>
       <c r="L14" t="n">
         <v>8.444444444444445</v>
       </c>
       <c r="M14" t="n">
-        <v>10.58265501065393</v>
+        <v>10.58262742970309</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F15" t="n">
-        <v>10.39740217185628</v>
+        <v>10.39740191841817</v>
       </c>
       <c r="G15" t="n">
         <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>1.155266907984031</v>
+        <v>1.155266879824241</v>
       </c>
       <c r="I15" t="n">
-        <v>103974.0217185628</v>
+        <v>103974.0191841817</v>
       </c>
       <c r="J15" t="n">
-        <v>1103974.021718563</v>
+        <v>1103974.019184182</v>
       </c>
       <c r="K15" t="n">
-        <v>20795.02802235678</v>
+        <v>20795.02467462141</v>
       </c>
       <c r="L15" t="n">
         <v>13.11111111111111</v>
       </c>
       <c r="M15" t="n">
-        <v>17.79472326915197</v>
+        <v>17.79471418372441</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F16" t="n">
-        <v>10.39740217185628</v>
+        <v>10.39740191841817</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.155266907984031</v>
+        <v>1.155266879824241</v>
       </c>
       <c r="I16" t="n">
-        <v>103974.0217185628</v>
+        <v>103974.0191841817</v>
       </c>
       <c r="J16" t="n">
-        <v>1103974.021718563</v>
+        <v>1103974.019184182</v>
       </c>
       <c r="K16" t="n">
-        <v>20795.02802235678</v>
+        <v>20795.02467462141</v>
       </c>
       <c r="L16" t="n">
         <v>13.11111111111111</v>
       </c>
       <c r="M16" t="n">
-        <v>17.79472326915197</v>
+        <v>17.79471418372441</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F17" t="n">
-        <v>9.905927717736759</v>
+        <v>9.905964931152971</v>
       </c>
       <c r="G17" t="n">
         <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>1.100658635304084</v>
+        <v>1.100662770128108</v>
       </c>
       <c r="I17" t="n">
-        <v>99059.27717736759</v>
+        <v>99059.64931152971</v>
       </c>
       <c r="J17" t="n">
-        <v>1099059.277177368</v>
+        <v>1099059.64931153</v>
       </c>
       <c r="K17" t="n">
-        <v>20100.69946756585</v>
+        <v>20100.70036289553</v>
       </c>
       <c r="L17" t="n">
         <v>9.222222222222221</v>
       </c>
       <c r="M17" t="n">
-        <v>10.58265501065394</v>
+        <v>10.58262742970311</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F18" t="n">
-        <v>9.905927717736759</v>
+        <v>9.905964931152971</v>
       </c>
       <c r="G18" t="n">
         <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>1.100658635304084</v>
+        <v>1.100662770128108</v>
       </c>
       <c r="I18" t="n">
-        <v>99059.27717736759</v>
+        <v>99059.64931152971</v>
       </c>
       <c r="J18" t="n">
-        <v>1099059.277177368</v>
+        <v>1099059.64931153</v>
       </c>
       <c r="K18" t="n">
-        <v>20100.69946756585</v>
+        <v>20100.70036289553</v>
       </c>
       <c r="L18" t="n">
         <v>9.222222222222221</v>
       </c>
       <c r="M18" t="n">
-        <v>10.58265501065394</v>
+        <v>10.58262742970311</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>46.15384615384615</v>
       </c>
       <c r="F19" t="n">
-        <v>9.665469717745902</v>
+        <v>9.665493867592421</v>
       </c>
       <c r="G19" t="n">
         <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7434976705958386</v>
+        <v>0.74349952827634</v>
       </c>
       <c r="I19" t="n">
-        <v>96654.69717745902</v>
+        <v>96654.9386759242</v>
       </c>
       <c r="J19" t="n">
-        <v>1096654.697177459</v>
+        <v>1096654.938675924</v>
       </c>
       <c r="K19" t="n">
-        <v>30806.76261850062</v>
+        <v>30806.76332421397</v>
       </c>
       <c r="L19" t="n">
         <v>9.923076923076923</v>
       </c>
       <c r="M19" t="n">
-        <v>19.65667288277962</v>
+        <v>19.65665215253912</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>46.15384615384615</v>
       </c>
       <c r="F20" t="n">
-        <v>9.665469717745902</v>
+        <v>9.665493867592421</v>
       </c>
       <c r="G20" t="n">
         <v>13</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7434976705958386</v>
+        <v>0.74349952827634</v>
       </c>
       <c r="I20" t="n">
-        <v>96654.69717745902</v>
+        <v>96654.9386759242</v>
       </c>
       <c r="J20" t="n">
-        <v>1096654.697177459</v>
+        <v>1096654.938675924</v>
       </c>
       <c r="K20" t="n">
-        <v>30806.76261850062</v>
+        <v>30806.76332421397</v>
       </c>
       <c r="L20" t="n">
         <v>9.923076923076923</v>
       </c>
       <c r="M20" t="n">
-        <v>19.65667288277962</v>
+        <v>19.65665215253912</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>46.15384615384615</v>
       </c>
       <c r="F21" t="n">
-        <v>4.879034560456523</v>
+        <v>4.879004863383947</v>
       </c>
       <c r="G21" t="n">
         <v>13</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3753103508043479</v>
+        <v>0.3753080664141498</v>
       </c>
       <c r="I21" t="n">
-        <v>48790.34560456523</v>
+        <v>48790.04863383947</v>
       </c>
       <c r="J21" t="n">
-        <v>1048790.345604565</v>
+        <v>1048790.048633839</v>
       </c>
       <c r="K21" t="n">
-        <v>28126.06758329614</v>
+        <v>28126.057046539</v>
       </c>
       <c r="L21" t="n">
         <v>8.384615384615385</v>
       </c>
       <c r="M21" t="n">
-        <v>14.77770008687219</v>
+        <v>14.77768771534723</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>46.15384615384615</v>
       </c>
       <c r="F22" t="n">
-        <v>2.825621309645369</v>
+        <v>2.825624549488269</v>
       </c>
       <c r="G22" t="n">
         <v>13</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2173554853573361</v>
+        <v>0.2173557345760207</v>
       </c>
       <c r="I22" t="n">
-        <v>28256.21309645369</v>
+        <v>28256.24549488269</v>
       </c>
       <c r="J22" t="n">
-        <v>1028256.213096454</v>
+        <v>1028256.245494883</v>
       </c>
       <c r="K22" t="n">
-        <v>28870.29001336155</v>
+        <v>28870.28598582492</v>
       </c>
       <c r="L22" t="n">
         <v>8.692307692307692</v>
       </c>
       <c r="M22" t="n">
-        <v>19.65667288277962</v>
+        <v>19.65665215253914</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1517,28 +1517,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.26326053529476</v>
+        <v>-5.263286409898626</v>
       </c>
       <c r="G23" t="n">
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3759471810924829</v>
+        <v>-0.3759490292784733</v>
       </c>
       <c r="I23" t="n">
-        <v>-52632.6053529476</v>
+        <v>-52632.86409898626</v>
       </c>
       <c r="J23" t="n">
-        <v>947367.3946470524</v>
+        <v>947367.1359010137</v>
       </c>
       <c r="K23" t="n">
-        <v>30071.089549607</v>
+        <v>30071.07890040205</v>
       </c>
       <c r="L23" t="n">
         <v>9.642857142857142</v>
       </c>
       <c r="M23" t="n">
-        <v>24.96389817562994</v>
+        <v>24.96387881476338</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.26326053529476</v>
+        <v>-5.263286409898626</v>
       </c>
       <c r="G24" t="n">
         <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3759471810924829</v>
+        <v>-0.3759490292784733</v>
       </c>
       <c r="I24" t="n">
-        <v>-52632.6053529476</v>
+        <v>-52632.86409898626</v>
       </c>
       <c r="J24" t="n">
-        <v>947367.3946470524</v>
+        <v>947367.1359010137</v>
       </c>
       <c r="K24" t="n">
-        <v>30071.089549607</v>
+        <v>30071.07890040205</v>
       </c>
       <c r="L24" t="n">
         <v>9.642857142857142</v>
       </c>
       <c r="M24" t="n">
-        <v>24.96389817562994</v>
+        <v>24.96387881476338</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,28 +1613,28 @@
         <v>36.36363636363637</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.463445611048664</v>
+        <v>-5.463449392946495</v>
       </c>
       <c r="G25" t="n">
         <v>11</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4966768737316967</v>
+        <v>-0.4966772175405904</v>
       </c>
       <c r="I25" t="n">
-        <v>-54634.45611048664</v>
+        <v>-54634.49392946495</v>
       </c>
       <c r="J25" t="n">
-        <v>945365.5438895134</v>
+        <v>945365.506070535</v>
       </c>
       <c r="K25" t="n">
-        <v>23630.17205519007</v>
+        <v>23630.17008980492</v>
       </c>
       <c r="L25" t="n">
         <v>9.363636363636363</v>
       </c>
       <c r="M25" t="n">
-        <v>23.38326740444044</v>
+        <v>23.38325819366829</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -1661,28 +1661,28 @@
         <v>36.36363636363637</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.463445611048664</v>
+        <v>-5.463449392946495</v>
       </c>
       <c r="G26" t="n">
         <v>11</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4966768737316967</v>
+        <v>-0.4966772175405904</v>
       </c>
       <c r="I26" t="n">
-        <v>-54634.45611048664</v>
+        <v>-54634.49392946495</v>
       </c>
       <c r="J26" t="n">
-        <v>945365.5438895134</v>
+        <v>945365.506070535</v>
       </c>
       <c r="K26" t="n">
-        <v>23630.17205519007</v>
+        <v>23630.17008980492</v>
       </c>
       <c r="L26" t="n">
         <v>9.363636363636363</v>
       </c>
       <c r="M26" t="n">
-        <v>23.38326740444044</v>
+        <v>23.38325819366829</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.926535969584889</v>
+        <v>-5.926573412408493</v>
       </c>
       <c r="G27" t="n">
         <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3292519983102716</v>
+        <v>-0.3292540784671385</v>
       </c>
       <c r="I27" t="n">
-        <v>-59265.35969584889</v>
+        <v>-59265.73412408493</v>
       </c>
       <c r="J27" t="n">
-        <v>940734.6403041511</v>
+        <v>940734.2658759151</v>
       </c>
       <c r="K27" t="n">
-        <v>36919.85978223611</v>
+        <v>36919.85161623633</v>
       </c>
       <c r="L27" t="n">
         <v>10.38888888888889</v>
       </c>
       <c r="M27" t="n">
-        <v>26.40343616744915</v>
+        <v>26.4034558990256</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.926535969584889</v>
+        <v>-5.926573412408493</v>
       </c>
       <c r="G28" t="n">
         <v>18</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3292519983102716</v>
+        <v>-0.3292540784671385</v>
       </c>
       <c r="I28" t="n">
-        <v>-59265.35969584889</v>
+        <v>-59265.73412408493</v>
       </c>
       <c r="J28" t="n">
-        <v>940734.6403041511</v>
+        <v>940734.2658759151</v>
       </c>
       <c r="K28" t="n">
-        <v>36919.85978223611</v>
+        <v>36919.85161623633</v>
       </c>
       <c r="L28" t="n">
         <v>10.38888888888889</v>
       </c>
       <c r="M28" t="n">
-        <v>26.40343616744915</v>
+        <v>26.4034558990256</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.076710578844499</v>
+        <v>-7.076737486159732</v>
       </c>
       <c r="G29" t="n">
         <v>18</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3931505877135832</v>
+        <v>-0.3931520825644295</v>
       </c>
       <c r="I29" t="n">
-        <v>-70767.10578844498</v>
+        <v>-70767.37486159732</v>
       </c>
       <c r="J29" t="n">
-        <v>929232.894211555</v>
+        <v>929232.6251384027</v>
       </c>
       <c r="K29" t="n">
-        <v>36763.71009264301</v>
+        <v>36763.70335329085</v>
       </c>
       <c r="L29" t="n">
         <v>10.5</v>
       </c>
       <c r="M29" t="n">
-        <v>27.30325313412942</v>
+        <v>27.30326474034992</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F30" t="n">
-        <v>-11.17200225941328</v>
+        <v>-11.17204328255101</v>
       </c>
       <c r="G30" t="n">
         <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.798000161386663</v>
+        <v>-0.7980030916107861</v>
       </c>
       <c r="I30" t="n">
-        <v>-111720.0225941328</v>
+        <v>-111720.43282551</v>
       </c>
       <c r="J30" t="n">
-        <v>888279.9774058672</v>
+        <v>888279.56717449</v>
       </c>
       <c r="K30" t="n">
-        <v>28303.54551172236</v>
+        <v>28303.53127660732</v>
       </c>
       <c r="L30" t="n">
         <v>8.5</v>
       </c>
       <c r="M30" t="n">
-        <v>24.96389817562996</v>
+        <v>24.96387881476339</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>36.36363636363637</v>
       </c>
       <c r="F31" t="n">
-        <v>-11.35970176814917</v>
+        <v>-11.35972204108955</v>
       </c>
       <c r="G31" t="n">
         <v>11</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.032700160740833</v>
+        <v>-1.032702003735414</v>
       </c>
       <c r="I31" t="n">
-        <v>-113597.0176814917</v>
+        <v>-113597.2204108955</v>
       </c>
       <c r="J31" t="n">
-        <v>886402.9823185083</v>
+        <v>886402.7795891045</v>
       </c>
       <c r="K31" t="n">
-        <v>22141.30425825898</v>
+        <v>22141.29899601834</v>
       </c>
       <c r="L31" t="n">
         <v>7.909090909090909</v>
       </c>
       <c r="M31" t="n">
-        <v>23.38326740444043</v>
+        <v>23.38325819366831</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F32" t="n">
-        <v>-13.96795887546826</v>
+        <v>-13.96798458910956</v>
       </c>
       <c r="G32" t="n">
         <v>21</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6651408988318217</v>
+        <v>-0.6651421232909314</v>
       </c>
       <c r="I32" t="n">
-        <v>-139679.5887546826</v>
+        <v>-139679.8458910956</v>
       </c>
       <c r="J32" t="n">
-        <v>860320.4112453174</v>
+        <v>860320.1541089044</v>
       </c>
       <c r="K32" t="n">
-        <v>39252.74946218758</v>
+        <v>39252.74493458439</v>
       </c>
       <c r="L32" t="n">
         <v>10.52380952380952</v>
       </c>
       <c r="M32" t="n">
-        <v>26.42417719637527</v>
+        <v>26.42419692239094</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F33" t="n">
-        <v>-13.96795887546826</v>
+        <v>-13.96798458910956</v>
       </c>
       <c r="G33" t="n">
         <v>21</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6651408988318217</v>
+        <v>-0.6651421232909314</v>
       </c>
       <c r="I33" t="n">
-        <v>-139679.5887546826</v>
+        <v>-139679.8458910956</v>
       </c>
       <c r="J33" t="n">
-        <v>860320.4112453174</v>
+        <v>860320.1541089044</v>
       </c>
       <c r="K33" t="n">
-        <v>39252.74946218758</v>
+        <v>39252.74493458439</v>
       </c>
       <c r="L33" t="n">
         <v>10.52380952380952</v>
       </c>
       <c r="M33" t="n">
-        <v>26.42417719637527</v>
+        <v>26.42419692239094</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F34" t="n">
-        <v>-15.01981627547027</v>
+        <v>-15.01983245845331</v>
       </c>
       <c r="G34" t="n">
         <v>21</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7152293464509655</v>
+        <v>-0.7152301170692054</v>
       </c>
       <c r="I34" t="n">
-        <v>-150198.1627547027</v>
+        <v>-150198.3245845331</v>
       </c>
       <c r="J34" t="n">
-        <v>849801.8372452973</v>
+        <v>849801.6754154669</v>
       </c>
       <c r="K34" t="n">
-        <v>39089.60330444677</v>
+        <v>39089.60025171823</v>
       </c>
       <c r="L34" t="n">
         <v>10.61904761904762</v>
       </c>
       <c r="M34" t="n">
-        <v>27.32374057608406</v>
+        <v>27.32375217903372</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F35" t="n">
-        <v>-17.10182211348048</v>
+        <v>-17.1018536881491</v>
       </c>
       <c r="G35" t="n">
         <v>22</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.777355550612749</v>
+        <v>-0.7773569858249588</v>
       </c>
       <c r="I35" t="n">
-        <v>-171018.2211348048</v>
+        <v>-171018.536881491</v>
       </c>
       <c r="J35" t="n">
-        <v>828981.7788651952</v>
+        <v>828981.463118509</v>
       </c>
       <c r="K35" t="n">
-        <v>40120.62962253331</v>
+        <v>40120.62271321522</v>
       </c>
       <c r="L35" t="n">
         <v>10.18181818181818</v>
       </c>
       <c r="M35" t="n">
-        <v>26.42417719637526</v>
+        <v>26.42419692239095</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F36" t="n">
-        <v>-17.10182211348048</v>
+        <v>-17.1018536881491</v>
       </c>
       <c r="G36" t="n">
         <v>22</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.777355550612749</v>
+        <v>-0.7773569858249588</v>
       </c>
       <c r="I36" t="n">
-        <v>-171018.2211348048</v>
+        <v>-171018.536881491</v>
       </c>
       <c r="J36" t="n">
-        <v>828981.7788651952</v>
+        <v>828981.463118509</v>
       </c>
       <c r="K36" t="n">
-        <v>40120.62962253331</v>
+        <v>40120.62271321522</v>
       </c>
       <c r="L36" t="n">
         <v>10.18181818181818</v>
       </c>
       <c r="M36" t="n">
-        <v>26.42417719637526</v>
+        <v>26.42419692239095</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F37" t="n">
-        <v>-18.11536382092875</v>
+        <v>-18.1153861289993</v>
       </c>
       <c r="G37" t="n">
         <v>22</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8234256282240342</v>
+        <v>-0.8234266422272412</v>
       </c>
       <c r="I37" t="n">
-        <v>-181153.6382092875</v>
+        <v>-181153.861289993</v>
       </c>
       <c r="J37" t="n">
-        <v>818846.3617907125</v>
+        <v>818846.138710007</v>
       </c>
       <c r="K37" t="n">
-        <v>39963.4263407197</v>
+        <v>39963.42086544209</v>
       </c>
       <c r="L37" t="n">
         <v>10.27272727272727</v>
       </c>
       <c r="M37" t="n">
-        <v>27.32374057608405</v>
+        <v>27.32375217903368</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>-18.21854294989503</v>
+        <v>-18.21858972728694</v>
       </c>
       <c r="G38" t="n">
         <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9109271474947518</v>
+        <v>-0.9109294863643468</v>
       </c>
       <c r="I38" t="n">
-        <v>-182185.4294989504</v>
+        <v>-182185.8972728694</v>
       </c>
       <c r="J38" t="n">
-        <v>817814.5705010496</v>
+        <v>817814.1027271306</v>
       </c>
       <c r="K38" t="n">
-        <v>41942.14355544751</v>
+        <v>41942.12234466581</v>
       </c>
       <c r="L38" t="n">
         <v>7.9</v>
       </c>
       <c r="M38" t="n">
-        <v>36.08290330837139</v>
+        <v>36.08289416256587</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>30</v>
       </c>
       <c r="F39" t="n">
-        <v>-18.21854294989503</v>
+        <v>-18.21858972728694</v>
       </c>
       <c r="G39" t="n">
         <v>20</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9109271474947518</v>
+        <v>-0.9109294863643468</v>
       </c>
       <c r="I39" t="n">
-        <v>-182185.4294989504</v>
+        <v>-182185.8972728694</v>
       </c>
       <c r="J39" t="n">
-        <v>817814.5705010496</v>
+        <v>817814.1027271306</v>
       </c>
       <c r="K39" t="n">
-        <v>41942.14355544751</v>
+        <v>41942.12234466581</v>
       </c>
       <c r="L39" t="n">
         <v>7.9</v>
       </c>
       <c r="M39" t="n">
-        <v>36.08290330837139</v>
+        <v>36.08289416256587</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>21.42857142857143</v>
       </c>
       <c r="F40" t="n">
-        <v>-19.95447025452879</v>
+        <v>-19.95448077032935</v>
       </c>
       <c r="G40" t="n">
         <v>14</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.425319303894913</v>
+        <v>-1.425320055023525</v>
       </c>
       <c r="I40" t="n">
-        <v>-199544.7025452879</v>
+        <v>-199544.8077032935</v>
       </c>
       <c r="J40" t="n">
-        <v>800455.2974547121</v>
+        <v>800455.1922967065</v>
       </c>
       <c r="K40" t="n">
-        <v>25312.17507938868</v>
+        <v>25312.17197953994</v>
       </c>
       <c r="L40" t="n">
         <v>9.642857142857142</v>
       </c>
       <c r="M40" t="n">
-        <v>20.0871380906465</v>
+        <v>20.08714584198619</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>21.42857142857143</v>
       </c>
       <c r="F41" t="n">
-        <v>-22.24278630127095</v>
+        <v>-22.24279651644913</v>
       </c>
       <c r="G41" t="n">
         <v>14</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.588770450090782</v>
+        <v>-1.588771179746367</v>
       </c>
       <c r="I41" t="n">
-        <v>-222427.8630127095</v>
+        <v>-222427.9651644913</v>
       </c>
       <c r="J41" t="n">
-        <v>777572.1369872905</v>
+        <v>777572.0348355087</v>
       </c>
       <c r="K41" t="n">
-        <v>25190.38204782508</v>
+        <v>25190.3789693695</v>
       </c>
       <c r="L41" t="n">
         <v>9.785714285714286</v>
       </c>
       <c r="M41" t="n">
-        <v>22.37166147164906</v>
+        <v>22.37166900139589</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>30.76923076923077</v>
       </c>
       <c r="F42" t="n">
-        <v>-22.26773020735961</v>
+        <v>-22.26774175079408</v>
       </c>
       <c r="G42" t="n">
         <v>26</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.8564511618215233</v>
+        <v>-0.8564516057997723</v>
       </c>
       <c r="I42" t="n">
-        <v>-222677.302073596</v>
+        <v>-222677.4175079408</v>
       </c>
       <c r="J42" t="n">
-        <v>777322.697926404</v>
+        <v>777322.5824920592</v>
       </c>
       <c r="K42" t="n">
-        <v>45673.14958479366</v>
+        <v>45673.15094116585</v>
       </c>
       <c r="L42" t="n">
         <v>8.307692307692308</v>
       </c>
       <c r="M42" t="n">
-        <v>31.76996667766071</v>
+        <v>31.76999025193898</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>30.76923076923077</v>
       </c>
       <c r="F43" t="n">
-        <v>-22.26773020735961</v>
+        <v>-22.26774175079408</v>
       </c>
       <c r="G43" t="n">
         <v>26</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.8564511618215233</v>
+        <v>-0.8564516057997723</v>
       </c>
       <c r="I43" t="n">
-        <v>-222677.302073596</v>
+        <v>-222677.4175079408</v>
       </c>
       <c r="J43" t="n">
-        <v>777322.697926404</v>
+        <v>777322.5824920592</v>
       </c>
       <c r="K43" t="n">
-        <v>45673.14958479366</v>
+        <v>45673.15094116585</v>
       </c>
       <c r="L43" t="n">
         <v>8.307692307692308</v>
       </c>
       <c r="M43" t="n">
-        <v>31.76996667766071</v>
+        <v>31.76999025193898</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>21.42857142857143</v>
       </c>
       <c r="F44" t="n">
-        <v>-23.19347280787324</v>
+        <v>-23.19347456833103</v>
       </c>
       <c r="G44" t="n">
         <v>14</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.656676629133803</v>
+        <v>-1.656676754880788</v>
       </c>
       <c r="I44" t="n">
-        <v>-231934.7280787324</v>
+        <v>-231934.7456833103</v>
       </c>
       <c r="J44" t="n">
-        <v>768065.2719212676</v>
+        <v>768065.2543166897</v>
       </c>
       <c r="K44" t="n">
-        <v>25093.63388997882</v>
+        <v>25093.63167672128</v>
       </c>
       <c r="L44" t="n">
         <v>9.928571428571429</v>
       </c>
       <c r="M44" t="n">
-        <v>23.3207723059801</v>
+        <v>23.32077142764516</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>30.76923076923077</v>
       </c>
       <c r="F45" t="n">
-        <v>-23.218111741165</v>
+        <v>-23.21811481631165</v>
       </c>
       <c r="G45" t="n">
         <v>26</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8930042977371154</v>
+        <v>-0.8930044160119865</v>
       </c>
       <c r="I45" t="n">
-        <v>-232181.11741165</v>
+        <v>-232181.1481631165</v>
       </c>
       <c r="J45" t="n">
-        <v>767818.88258835</v>
+        <v>767818.8518368835</v>
       </c>
       <c r="K45" t="n">
-        <v>45482.96562747855</v>
+        <v>45482.96868262125</v>
       </c>
       <c r="L45" t="n">
         <v>8.384615384615385</v>
       </c>
       <c r="M45" t="n">
-        <v>32.60417059185823</v>
+        <v>32.60418656869427</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>-23.31926216676431</v>
+        <v>-23.31932049672107</v>
       </c>
       <c r="G46" t="n">
         <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.165963108338215</v>
+        <v>-1.165966024836053</v>
       </c>
       <c r="I46" t="n">
-        <v>-233192.6216676431</v>
+        <v>-233193.2049672107</v>
       </c>
       <c r="J46" t="n">
-        <v>766807.3783323569</v>
+        <v>766806.7950327893</v>
       </c>
       <c r="K46" t="n">
-        <v>39557.244376616</v>
+        <v>39557.21851299029</v>
       </c>
       <c r="L46" t="n">
         <v>7.1</v>
       </c>
       <c r="M46" t="n">
-        <v>36.0829033083714</v>
+        <v>36.08289416256591</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
